--- a/docs/requirements/Top_50_Global_Online_Sources.xlsx
+++ b/docs/requirements/Top_50_Global_Online_Sources.xlsx
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="16" min="1" max="1"/>
@@ -563,14 +563,14 @@
     <row r="1" ht="20" customHeight="1" s="16">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Top 51 Global Online Sources</t>
+          <t>Top 52 Global Online Sources</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ranked by daily user count where published; by documented proxy where not. Compiled July 2026. Rev. 2 - social expanded to 8 at user request (X added; Instagram was already present at #2). Rev. 3 (2026-09-29): Hacker News and Stack Overflow moved from Developer to a new Forums section, aligning with the product's 8-category taxonomy. Read the Methodology tab before citing any figure.</t>
+          <t>Ranked by daily user count where published; by documented proxy where not. Compiled July 2026. Rev. 2 - social expanded to 8 at user request (X added; Instagram was already present at #2). Rev. 3 (2026-09-29): Hacker News and Stack Overflow moved from Developer to a new Forums section, aligning with the product's 8-category taxonomy. Rev. 4 (2026-09-29): Reddit added as #52 in the Forums section at user request (130.3M daily active uniques, Q2 2026; an unaudited company-reported KPI). Read the Methodology tab before citing any figure.</t>
         </is>
       </c>
     </row>
@@ -581,10 +581,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="16">
+    <row r="5" ht="39" customHeight="1" s="16">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Ranked by largest published audience figure. Only Meta (family-level DAP), Snap, and Reddit publish an audited DAU; none of the eight below publish a per-platform DAU. X was added at user request and sits outside the traffic-ranked top 7 - it is the weakest-evidenced row in this workbook. Metric type is labeled per row and must not be blended.</t>
+          <t>Ranked by largest published audience figure. Only Meta (family-level DAP) and Snap publish an audited DAU, and Reddit an unaudited company-reported DAUq (Rev. 4 correction; Reddit is #52 in Forums); none of the eight below publish a per-platform DAU. X was added at user request and sits outside the traffic-ranked top 7 - it is the weakest-evidenced row in this workbook. Metric type is labeled per row and must not be blended.</t>
         </is>
       </c>
     </row>
@@ -3086,14 +3086,14 @@
     <row r="72" ht="22" customHeight="1" s="16">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>7. FORUMS (2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1" s="16">
+          <t>7. FORUMS (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="65" customHeight="1" s="16">
       <c r="A73" s="15" t="inlineStr">
         <is>
-          <t>Ranked by Similarweb monthly visits. Both rows moved here from Developer Communities in Rev. 3 (2026-09-29), with figures and credibility notes unchanged, to align with the product's 8-category taxonomy.</t>
+          <t>Ranked by Similarweb monthly visits. Both rows moved here from Developer Communities in Rev. 3 (2026-09-29), with figures and credibility notes unchanged, to align with the product's 8-category taxonomy. Reddit (#52) was added in Rev. 4 (2026-09-29) at user request. Its figure is Reddit's own daily active uniques (DAUq), not a Similarweb visit count, so it is listed last and must not be ranked against the two rows above.</t>
         </is>
       </c>
     </row>
@@ -3245,308 +3245,356 @@
         </is>
       </c>
     </row>
-    <row r="77" s="16"/>
-    <row r="78" ht="22" customHeight="1" s="16">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="77" ht="30" customHeight="1" s="16">
+      <c r="A77" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Daily active uniques (DAUq)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>130.3M</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>130300000</v>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Q2 2026 (quarter avg., ended 30 Jun 2026)</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Reddit Q2 2026 results (30 Jul 2026): Letter to Shareholders + Form 8-K Ex. 99.1; restated in Q2 2026 Form 10-Q</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Company-reported</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>ADDED AT USER REQUEST in Rev. 4 (2026-09-29). Reddit, Inc. is an NYSE-listed SEC registrant. The DAUq is an unaudited company KPI. 59.6% of it (77.7M) is logged-out users, and bots are removed only going forward. WAUq 514.6M. +18% YoY (Q2 2025: 110.4M).</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" s="16"/>
+    <row r="79" ht="22" customHeight="1" s="16">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>8. BLOGS AND NEWSLETTERS (5)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1" s="16">
-      <c r="A79" s="15" t="inlineStr">
+    <row r="80" ht="30" customHeight="1" s="16">
+      <c r="A80" s="15" t="inlineStr">
         <is>
           <t>The weakest-evidenced category by a wide margin. Nearly every figure is self-reported with a direct commercial incentive to inflate, and several widely-cited numbers (Morning Brew 4M, Stratechery 40K) are stale or fabricated. Ranked by subscriber or visit count as labeled.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1" s="16">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="81" ht="18" customHeight="1" s="16">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Metric Type</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E81" s="4" t="inlineStr">
         <is>
           <t>Value (numeric)</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>As-Of</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>Publisher of Figure</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>Figure Type</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>Credibility Basis</t>
         </is>
       </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1" s="16">
-      <c r="A81" s="5" t="n">
+    <row r="82" ht="30" customHeight="1" s="16">
+      <c r="A82" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>TLDR (13 newsletters)</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Free subscribers</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>7.2M+</t>
         </is>
       </c>
-      <c r="E81" s="8" t="n">
+      <c r="E82" s="8" t="n">
         <v>7200000</v>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>26 Jun 2026</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>advertise.tldr.tech rate card</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>Self-reported</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>RATE-CARD figure - direct commercial incentive to inflate. TLDR Tech 1.6M; TLDR AI 1.1M</t>
         </is>
       </c>
-      <c r="J81" s="13" t="inlineStr">
+      <c r="J82" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1" s="16">
-      <c r="A82" s="9" t="n">
+    <row r="83" ht="30" customHeight="1" s="16">
+      <c r="A83" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>Substack (platform-level)</t>
         </is>
       </c>
-      <c r="C82" s="11" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>Paid subscriptions, platform-wide</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
         <is>
           <t>5M</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="E83" s="12" t="n">
         <v>5000000</v>
       </c>
-      <c r="F82" s="11" t="inlineStr">
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>11 Mar 2025</t>
         </is>
       </c>
-      <c r="G82" s="11" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
         <is>
           <t>The Substack Post</t>
         </is>
       </c>
-      <c r="H82" s="11" t="inlineStr">
+      <c r="H83" s="11" t="inlineStr">
         <is>
           <t>Self-reported</t>
         </is>
       </c>
-      <c r="I82" s="11" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>STALE. Substack DECLINED to give an updated figure to Press Gazette in Feb 2026. Circulating '8.4M' has no source</t>
         </is>
       </c>
-      <c r="J82" s="13" t="inlineStr">
+      <c r="J83" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1" s="16">
-      <c r="A83" s="5" t="n">
+    <row r="84" ht="30" customHeight="1" s="16">
+      <c r="A84" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Ars Technica</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Monthly visits (Similarweb)</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>8.3M</t>
         </is>
       </c>
-      <c r="E83" s="8" t="n">
+      <c r="E84" s="8" t="n">
         <v>8300000</v>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>Similarweb</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>Vendor-estimated</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Conde Nast. 59% bounce rate, 1.96 pages/visit - this is not 8.3M distinct readers</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1" s="16">
-      <c r="A84" s="9" t="n">
+    <row r="85" ht="30" customHeight="1" s="16">
+      <c r="A85" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>One Useful Thing (Ethan Mollick)</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>Subscribers (free + paid)</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>453K+</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="E85" s="12" t="n">
         <v>453000</v>
       </c>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>12 Jul 2026</t>
         </is>
       </c>
-      <c r="G84" s="11" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
         <is>
           <t>Substack platform profile</t>
         </is>
       </c>
-      <c r="H84" s="11" t="inlineStr">
+      <c r="H85" s="11" t="inlineStr">
         <is>
           <t>Operator-reported</t>
         </is>
       </c>
-      <c r="I84" s="11" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>Wharton professor. Platform-generated count - not self-asserted. Freshest figure in category</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="30" customHeight="1" s="16">
-      <c r="A85" s="5" t="n">
+    <row r="86" ht="30" customHeight="1" s="16">
+      <c r="A86" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>Platformer (Casey Newton)</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Free subscribers</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>200K free</t>
         </is>
       </c>
-      <c r="E85" s="8" t="n">
+      <c r="E86" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="F85" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>23 Sep 2025</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
         <is>
           <t>Platformer, 'Year Five' post</t>
         </is>
       </c>
-      <c r="H85" s="7" t="inlineStr">
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>Self-reported</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Most transparent free/paid disclosure in the set - explicitly separates the two</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3557,10 +3605,10 @@
     <mergeCell ref="A44:J44"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A80:J80"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A79:J79"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A65:J65"/>
@@ -3595,7 +3643,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="117" customHeight="1" s="16">
+    <row r="3" ht="156" customHeight="1" s="16">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>The central problem</t>
@@ -3603,12 +3651,12 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>The brief asked for ranking by DAILY USER COUNT. Only three organizations in this entire list publish an audited daily active user figure: Meta (family-level DAP, 3.56B, Mar 2026), Snap (483M DAU, Q1 2026), and Reddit (126.8M daily active uniques, Q1 2026). Two others publish a true daily number without audit: PubMed (3.5M weekday users) and the Internet Archive (~800K daily visitors).
+          <t>The brief asked for ranking by DAILY USER COUNT. Only three organizations in this entire list publish a daily active user figure: Meta (family-level DAP, 3.56B, Mar 2026) and Snap (483M DAU, Q1 2026), whose figures are audited, and Reddit (130.3M daily active uniques, Q2 2026), whose figure is SEC-disclosed but an unaudited company-reported KPI (Rev. 4, 2026-09-29: corrected from "audited", and updated from the Q1 2026 figure of 126.8M). Two others publish a true daily number without audit: PubMed (3.5M weekday users) and the Internet Archive (~800K daily visitors).
 Every other source on this list either does not measure DAU, does not publish it, or is a private company. Rather than invent daily numbers, each row is ranked on the best figure its publisher actually releases, and the METRIC TYPE column names that figure exactly. Do not compare values across metric types.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="143" customHeight="1" s="16">
+    <row r="4" ht="195" customHeight="1" s="16">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Metric types used</t>
@@ -3617,6 +3665,7 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>MAU - monthly active users (company-reported)
+Daily active uniques (DAUq) - Reddit's identified unique visitors in a 24 h period, logged-in and logged-out combined; quarterly average (Rev. 4)
 Monthly advertising reach - the audience an advertiser can buy; a proxy, not a user count
 Monthly visits - Similarweb panel-modeled sessions; NOT unique people
 Monthly unique devices - Wikimedia's server-side reader proxy
@@ -3626,7 +3675,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="156" customHeight="1" s="16">
+    <row r="5" ht="208" customHeight="1" s="16">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Figure-type reliability ladder</t>
@@ -3634,7 +3683,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>AUDITED (highest) - SEC filing, AAM audit, or audited charity accounts. Only 3 rows qualify: GitLab (10-K), Our World in Data (UK charity accounts), and Wired (AAM, excluded from the 50 but noted).
+          <t>AUDITED (highest) - SEC filing, AAM audit, or audited charity accounts. Only 3 rows qualify: GitLab (10-K), Our World in Data (UK charity accounts), and Wired (AAM, excluded from the 50 but noted). A user KPI stated inside an SEC filing is NOT audited (Rev. 4): Reddit's DAUq (10-Q) stays Company-reported, and the same caution applies to GitLab's 10-K registered-user count (not re-rated in Rev. 4).
 GOVERNMENT-REPORTED - GPO, Library of Congress, NLM. Official but measures machine + human traffic together.
 COMPANY-REPORTED - stated in earnings materials by a public issuer.
 OPERATOR-REPORTED - the platform's own server-side stats (Wikimedia, arXiv, Khan Academy).
@@ -3692,7 +3741,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="299" customHeight="1" s="16">
+    <row r="9" ht="364" customHeight="1" s="16">
       <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Notable exclusions worth knowing</t>
@@ -3703,8 +3752,9 @@
           <t>BROOKINGS INSTITUTION - almost certainly belongs in the policy category by size, but has published no traffic figure since a June 2023 marketing claim. Excluded on evidence grounds, not merit.
 npm and PyPI - 640B monthly package downloads and 2.56T annual requests respectively. Excluded because this is CI/CD and mirror traffic, not human audience.
 WIRED - 315,502 AAM-AUDITED paid digital subscriptions (31 Dec 2025). The single most rigorously evidenced audience number found anywhere in this research. Excluded from the 50 only because it is a magazine, not a blog or newsletter. If you need one number that survives adversarial scrutiny, use this one.
-SNAPCHAT (483M DAU) and REDDIT (126.8M DAU) - still excluded from social. Note the irony: the two platforms with the ONLY audited DAU figures did not make a list ranked by daily users, while X - which publishes nothing - did.
-X (formerly Twitter) - ADDED AT USER REQUEST in Rev. 2, taking social to 8. It did not qualify on the original traffic ranking and it is the lowest-confidence row in the workbook. If the brief's 'credible sources' gate were applied to social platforms the way it was applied to news outlets, X would fail it: there is no audited figure, no published methodology, and no independent verification of any user number since 2022. Both Snapchat (483M audited DAU) and Reddit (126.8M audited DAU) are better-evidenced AND better-documented than X. If the goal is a defensible list, swapping X for either of them is the stronger call.</t>
+SNAPCHAT (483M DAU) - still excluded from social. Note the irony: a platform with one of the ONLY audited DAU figures did not make a list ranked by daily users, while X - which publishes nothing - did.
+REDDIT - NO LONGER EXCLUDED (Rev. 4, 2026-09-29). Jennifer's decision ("can we add reddit to the source lis") added it as #52 in the Forums section, not Social. Earlier revisions called its DAU audited: the 130.3M DAUq (Q2 2026) is SEC-disclosed but an unaudited company-reported KPI.
+X (formerly Twitter) - ADDED AT USER REQUEST in Rev. 2, taking social to 8. It did not qualify on the original traffic ranking and it is the lowest-confidence row in the workbook. If the brief's 'credible sources' gate were applied to social platforms the way it was applied to news outlets, X would fail it: there is no audited figure, no published methodology, and no independent verification of any user number since 2022. Both Snapchat (483M audited DAU) and Reddit (130.3M unaudited DAUq; in the list as #52 in Forums since Rev. 4) are better-evidenced AND better-documented than X. If the goal is a defensible list, swapping X for Snapchat is the stronger call.</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3808,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1" s="16">
+    <row r="5" ht="104" customHeight="1" s="16">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>SEC EDGAR (10-K, 10-Q, 8-K)</t>
@@ -3771,7 +3821,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Legally binding disclosure. Used for: Meta DAP, Snap DAU, Reddit DAUq, GitLab registered users. The only figures with liability attached.</t>
+          <t>Legally binding disclosure. Used for: Meta DAP, Snap DAU, Reddit DAUq, GitLab registered users. The only figures with liability attached. Rev. 4 note: a user KPI inside a filing is not audited - Reddit's DAUq is SEC-disclosed but unaudited, so the Reddit row (#52) is Company-reported.</t>
         </is>
       </c>
     </row>
